--- a/Таблица истинности.xlsx
+++ b/Таблица истинности.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12750" windowHeight="9120"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="27">
   <si>
     <t>S</t>
   </si>
@@ -78,6 +78,33 @@
   </si>
   <si>
     <t>х</t>
+  </si>
+  <si>
+    <t>Таблица истинности для синхронного D-триггера</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>0-&gt;1</t>
+  </si>
+  <si>
+    <t>Таблица истинности для синхронного T-триггера</t>
+  </si>
+  <si>
+    <t>CLK</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Счетный режим</t>
+  </si>
+  <si>
+    <t>Таблица истинности для ассинхронного JK-триггера</t>
   </si>
 </sst>
 </file>
@@ -164,12 +191,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -178,6 +209,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -459,24 +506,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" customWidth="1"/>
     <col min="6" max="6" width="55.85546875" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" customWidth="1"/>
+    <col min="13" max="13" width="16.85546875" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="J1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="3"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -493,8 +553,20 @@
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>0</v>
       </c>
@@ -508,11 +580,23 @@
       <c r="E3" s="2">
         <v>0</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>0</v>
       </c>
@@ -526,9 +610,21 @@
       <c r="E4" s="2">
         <v>1</v>
       </c>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F4" s="6"/>
+      <c r="J4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -542,11 +638,23 @@
       <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -560,9 +668,21 @@
       <c r="E6" s="2">
         <v>1</v>
       </c>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="6"/>
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>0</v>
       </c>
@@ -576,11 +696,23 @@
       <c r="E7" s="2">
         <v>0</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>0</v>
       </c>
@@ -594,9 +726,21 @@
       <c r="E8" s="2">
         <v>0</v>
       </c>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="6"/>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1</v>
       </c>
@@ -610,11 +754,11 @@
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>1</v>
       </c>
@@ -628,19 +772,51 @@
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="F10" s="6"/>
+      <c r="J10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="J12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -657,8 +833,20 @@
       <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>0</v>
       </c>
@@ -672,11 +860,23 @@
       <c r="E14" s="2">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>0</v>
       </c>
@@ -690,9 +890,21 @@
       <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F15" s="6"/>
+      <c r="J15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>1</v>
       </c>
@@ -706,11 +918,15 @@
       <c r="E16" s="2">
         <v>1</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1</v>
       </c>
@@ -724,9 +940,13 @@
       <c r="E17" s="2">
         <v>1</v>
       </c>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="6"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>0</v>
       </c>
@@ -740,11 +960,11 @@
       <c r="E18" s="2">
         <v>0</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>0</v>
       </c>
@@ -758,9 +978,9 @@
       <c r="E19" s="2">
         <v>0</v>
       </c>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>1</v>
       </c>
@@ -774,11 +994,11 @@
       <c r="E20" s="2">
         <v>0</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>1</v>
       </c>
@@ -792,19 +1012,27 @@
       <c r="E21" s="2">
         <v>1</v>
       </c>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="F21" s="6"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="J24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -823,8 +1051,26 @@
       <c r="F25" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>0</v>
       </c>
@@ -840,11 +1086,29 @@
       <c r="E26" s="1">
         <v>0</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J26" s="9">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>0</v>
       </c>
@@ -860,9 +1124,25 @@
       <c r="E27" s="1">
         <v>1</v>
       </c>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F27" s="6"/>
+      <c r="J27" s="9">
+        <v>0</v>
+      </c>
+      <c r="K27" s="9">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="9">
+        <v>1</v>
+      </c>
+      <c r="N27" s="9">
+        <v>1</v>
+      </c>
+      <c r="O27" s="6"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>1</v>
       </c>
@@ -878,11 +1158,29 @@
       <c r="E28" s="2">
         <v>0</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J28" s="10">
+        <v>1</v>
+      </c>
+      <c r="K28" s="10">
+        <v>0</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="10">
+        <v>1</v>
+      </c>
+      <c r="N28" s="10">
+        <v>1</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>1</v>
       </c>
@@ -898,9 +1196,25 @@
       <c r="E29" s="2">
         <v>1</v>
       </c>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F29" s="6"/>
+      <c r="J29" s="10">
+        <v>1</v>
+      </c>
+      <c r="K29" s="10">
+        <v>0</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="10">
+        <v>0</v>
+      </c>
+      <c r="N29" s="10">
+        <v>1</v>
+      </c>
+      <c r="O29" s="6"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>0</v>
       </c>
@@ -916,11 +1230,29 @@
       <c r="E30" s="2">
         <v>1</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J30" s="10">
+        <v>1</v>
+      </c>
+      <c r="K30" s="10">
+        <v>1</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="10">
+        <v>0</v>
+      </c>
+      <c r="N30" s="10">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>0</v>
       </c>
@@ -936,9 +1268,25 @@
       <c r="E31" s="2">
         <v>1</v>
       </c>
-      <c r="F31" s="4"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F31" s="6"/>
+      <c r="J31" s="10">
+        <v>1</v>
+      </c>
+      <c r="K31" s="10">
+        <v>1</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="10">
+        <v>1</v>
+      </c>
+      <c r="N31" s="10">
+        <v>0</v>
+      </c>
+      <c r="O31" s="6"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>1</v>
       </c>
@@ -954,11 +1302,29 @@
       <c r="E32" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J32" s="10">
+        <v>0</v>
+      </c>
+      <c r="K32" s="10">
+        <v>1</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" s="10">
+        <v>0</v>
+      </c>
+      <c r="N32" s="10">
+        <v>1</v>
+      </c>
+      <c r="O32" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>1</v>
       </c>
@@ -974,9 +1340,25 @@
       <c r="E33" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F33" s="4"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F33" s="6"/>
+      <c r="J33" s="10">
+        <v>0</v>
+      </c>
+      <c r="K33" s="10">
+        <v>1</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="10">
+        <v>1</v>
+      </c>
+      <c r="N33" s="10">
+        <v>0</v>
+      </c>
+      <c r="O33" s="13"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
@@ -992,11 +1374,17 @@
       <c r="E34" s="2">
         <v>0</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="12"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
@@ -1012,16 +1400,29 @@
       <c r="E35" s="2">
         <v>1</v>
       </c>
-      <c r="F35" s="4"/>
+      <c r="F35" s="6"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="24">
+    <mergeCell ref="O34:O35"/>
+    <mergeCell ref="J24:O24"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="O28:O29"/>
+    <mergeCell ref="O30:O31"/>
+    <mergeCell ref="O32:O33"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="F28:F29"/>
     <mergeCell ref="F30:F31"/>
     <mergeCell ref="F32:F33"/>
     <mergeCell ref="F34:F35"/>
     <mergeCell ref="F26:F27"/>
+    <mergeCell ref="J1:M1"/>
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A12:F12"/>
@@ -1032,6 +1433,7 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F9:F10"/>
+    <mergeCell ref="J10:M10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
